--- a/docs/huong-dan/nhap-lieu-bang-excel/mau/mau-ton-kho.xlsx
+++ b/docs/huong-dan/nhap-lieu-bang-excel/mau/mau-ton-kho.xlsx
@@ -462,18 +462,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mỗi dòng = 1 dòng tồn kho (số THỜI ĐIỂM cuối ngày, không cộng dồn). Nhóm 'Đã ký HĐ' mới cần Đơn giá / Lịch giao (file HĐ scan đính kèm trên web).</t>
+          <t>Mỗi dòng = 1 dòng tồn kho (số THỜI ĐIỂM cuối ngày, không cộng dồn). Riêng nhóm 'Đã ký HĐ' là HỢP ĐỒNG có vòng đời: nhập MỘT LẦN, hệ thống tự tính vào tồn kho từ cột 'Ngày' (= ngày bắt đầu tồn kho) đến HẾT NGÀY TRƯỚC 'Ngày giao'; chưa giao thì để trống 'Ngày giao'. KHÔNG nhập lại hợp đồng đó cho các ngày sau. File HĐ scan đính kèm trên web.</t>
         </is>
       </c>
     </row>
@@ -520,25 +522,35 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>Mã HĐ/PL</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Số lượng</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Đơn giá</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Đơn giá bằng</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Lịch giao</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Ngày giao</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Tồn kho nguyên liệu chưa sản xuất (quy khô)</t>
         </is>
@@ -555,25 +567,35 @@
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>chỉ nhóm đã ký HĐ</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>tấn</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>chỉ nhóm đã ký HĐ</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>VND | USD</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>dd/mm/yyyy</t>
-        </is>
-      </c>
       <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>dd/mm/yyyy · dự kiến</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>dd/mm/yyyy · để trống nếu chưa giao</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>tấn</t>
         </is>
@@ -591,7 +613,7 @@
     <dataValidation sqref="D7:D506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SVR CV 50,SVR CV60,SVR L,SVR 3L Mix,SVR 3L,SVR 5S,SVR 5,SVR 10 Mix,SVR 10 / CSR 10,SVR 20 / CSR 20,RSS 3,RSS 1,LATEX,Skim Block,SVR 10CV / 20CV,Chủng loại khác"</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H7:H506" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VND,USD"</formula1>
     </dataValidation>
   </dataValidations>
